--- a/output/yearly_population_iteration_43_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_43_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6436</v>
+        <v>6847</v>
       </c>
       <c r="C2" t="n">
-        <v>7201</v>
+        <v>7177</v>
       </c>
       <c r="D2" t="n">
-        <v>39034</v>
+        <v>41815</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4374</v>
+        <v>4523</v>
       </c>
       <c r="C3" t="n">
-        <v>4989</v>
+        <v>4982</v>
       </c>
       <c r="D3" t="n">
-        <v>18437</v>
+        <v>18768</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3307</v>
+        <v>3338</v>
       </c>
       <c r="C4" t="n">
-        <v>4347</v>
+        <v>6604</v>
       </c>
       <c r="D4" t="n">
-        <v>8484</v>
+        <v>8658</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2097</v>
+        <v>2156</v>
       </c>
       <c r="C5" t="n">
-        <v>2852</v>
+        <v>5361</v>
       </c>
       <c r="D5" t="n">
-        <v>2948</v>
+        <v>3239</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="C6" t="n">
-        <v>2228</v>
+        <v>2876</v>
       </c>
       <c r="D6" t="n">
-        <v>1153</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>616</v>
+        <v>591</v>
       </c>
       <c r="C7" t="n">
-        <v>1554</v>
+        <v>1388</v>
       </c>
       <c r="D7" t="n">
-        <v>652</v>
+        <v>661</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="C8" t="n">
-        <v>782</v>
+        <v>520</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>347</v>
+        <v>257</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7463</v>
+        <v>9356</v>
       </c>
       <c r="C2" t="n">
-        <v>8433</v>
+        <v>11572</v>
       </c>
       <c r="D2" t="n">
-        <v>50411</v>
+        <v>38523</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4323</v>
+        <v>4557</v>
       </c>
       <c r="C3" t="n">
-        <v>5275</v>
+        <v>5252</v>
       </c>
       <c r="D3" t="n">
-        <v>19999</v>
+        <v>20821</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3227</v>
+        <v>3276</v>
       </c>
       <c r="C4" t="n">
-        <v>4523</v>
+        <v>5703</v>
       </c>
       <c r="D4" t="n">
-        <v>9768</v>
+        <v>9864</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2337</v>
+        <v>2344</v>
       </c>
       <c r="C5" t="n">
-        <v>3495</v>
+        <v>5758</v>
       </c>
       <c r="D5" t="n">
-        <v>3761</v>
+        <v>3972</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1485</v>
+        <v>1497</v>
       </c>
       <c r="C6" t="n">
-        <v>2465</v>
+        <v>3945</v>
       </c>
       <c r="D6" t="n">
-        <v>1401</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>805</v>
+        <v>789</v>
       </c>
       <c r="C7" t="n">
-        <v>1857</v>
+        <v>2015</v>
       </c>
       <c r="D7" t="n">
-        <v>723</v>
+        <v>744</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="C8" t="n">
-        <v>1106</v>
+        <v>885</v>
       </c>
       <c r="D8" t="n">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C9" t="n">
-        <v>530</v>
+        <v>360</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>264</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1321,7 +1321,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9370</v>
+        <v>9530</v>
       </c>
       <c r="C2" t="n">
-        <v>9228</v>
+        <v>11231</v>
       </c>
       <c r="D2" t="n">
-        <v>40368</v>
+        <v>34956</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4552</v>
+        <v>5215</v>
       </c>
       <c r="C3" t="n">
-        <v>5837</v>
+        <v>6896</v>
       </c>
       <c r="D3" t="n">
-        <v>22579</v>
+        <v>21612</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3131</v>
+        <v>3250</v>
       </c>
       <c r="C4" t="n">
-        <v>4761</v>
+        <v>5339</v>
       </c>
       <c r="D4" t="n">
-        <v>11042</v>
+        <v>11047</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2399</v>
+        <v>2406</v>
       </c>
       <c r="C5" t="n">
-        <v>3822</v>
+        <v>5615</v>
       </c>
       <c r="D5" t="n">
-        <v>4475</v>
+        <v>4699</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1669</v>
+        <v>1663</v>
       </c>
       <c r="C6" t="n">
-        <v>2843</v>
+        <v>4586</v>
       </c>
       <c r="D6" t="n">
-        <v>1722</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>978</v>
+        <v>952</v>
       </c>
       <c r="C7" t="n">
-        <v>2106</v>
+        <v>2751</v>
       </c>
       <c r="D7" t="n">
-        <v>801</v>
+        <v>843</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>464</v>
+        <v>437</v>
       </c>
       <c r="C8" t="n">
-        <v>1389</v>
+        <v>1316</v>
       </c>
       <c r="D8" t="n">
-        <v>490</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="C9" t="n">
-        <v>744</v>
+        <v>546</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C10" t="n">
-        <v>362</v>
+        <v>269</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1632,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1674,7 +1674,7 @@
         <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8477</v>
+        <v>8834</v>
       </c>
       <c r="C2" t="n">
-        <v>6275</v>
+        <v>7816</v>
       </c>
       <c r="D2" t="n">
-        <v>33161</v>
+        <v>29002</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5576</v>
+        <v>6012</v>
       </c>
       <c r="C3" t="n">
-        <v>8630</v>
+        <v>10043</v>
       </c>
       <c r="D3" t="n">
-        <v>24094</v>
+        <v>23103</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2216</v>
+        <v>2223</v>
       </c>
       <c r="C4" t="n">
-        <v>6320</v>
+        <v>8260</v>
       </c>
       <c r="D4" t="n">
-        <v>10407</v>
+        <v>10459</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1542</v>
+        <v>1536</v>
       </c>
       <c r="C5" t="n">
-        <v>2786</v>
+        <v>4494</v>
       </c>
       <c r="D5" t="n">
-        <v>2890</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>903</v>
+        <v>879</v>
       </c>
       <c r="C6" t="n">
-        <v>2063</v>
+        <v>2695</v>
       </c>
       <c r="D6" t="n">
-        <v>784</v>
+        <v>826</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>428</v>
+        <v>403</v>
       </c>
       <c r="C7" t="n">
-        <v>1361</v>
+        <v>1289</v>
       </c>
       <c r="D7" t="n">
-        <v>480</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="C8" t="n">
-        <v>729</v>
+        <v>535</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>354</v>
+        <v>263</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1929,7 +1929,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1971,7 +1971,7 @@
         <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5317</v>
+        <v>5537</v>
       </c>
       <c r="C2" t="n">
-        <v>3122</v>
+        <v>4428</v>
       </c>
       <c r="D2" t="n">
-        <v>23357</v>
+        <v>20332</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5848</v>
+        <v>6188</v>
       </c>
       <c r="C3" t="n">
-        <v>6835</v>
+        <v>8236</v>
       </c>
       <c r="D3" t="n">
-        <v>23939</v>
+        <v>22796</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3031</v>
+        <v>3129</v>
       </c>
       <c r="C4" t="n">
-        <v>7517</v>
+        <v>9130</v>
       </c>
       <c r="D4" t="n">
-        <v>12392</v>
+        <v>12062</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1697</v>
+        <v>1689</v>
       </c>
       <c r="C5" t="n">
-        <v>4320</v>
+        <v>6134</v>
       </c>
       <c r="D5" t="n">
-        <v>3795</v>
+        <v>3965</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1077</v>
+        <v>1041</v>
       </c>
       <c r="C6" t="n">
-        <v>2418</v>
+        <v>3437</v>
       </c>
       <c r="D6" t="n">
-        <v>999</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>402</v>
+        <v>375</v>
       </c>
       <c r="C7" t="n">
-        <v>1673</v>
+        <v>1774</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>936</v>
+        <v>731</v>
       </c>
       <c r="D8" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>407</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
         <v>211</v>
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
@@ -2226,7 +2226,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2268,7 +2268,7 @@
         <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5869</v>
+        <v>5780</v>
       </c>
       <c r="C2" t="n">
-        <v>6571</v>
+        <v>12225</v>
       </c>
       <c r="D2" t="n">
-        <v>24305</v>
+        <v>25124</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4718</v>
+        <v>5023</v>
       </c>
       <c r="C3" t="n">
-        <v>4513</v>
+        <v>5759</v>
       </c>
       <c r="D3" t="n">
-        <v>22438</v>
+        <v>20929</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3667</v>
+        <v>3761</v>
       </c>
       <c r="C4" t="n">
-        <v>7026</v>
+        <v>8510</v>
       </c>
       <c r="D4" t="n">
-        <v>13899</v>
+        <v>13447</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2010</v>
+        <v>2027</v>
       </c>
       <c r="C5" t="n">
-        <v>5734</v>
+        <v>7445</v>
       </c>
       <c r="D5" t="n">
-        <v>5000</v>
+        <v>5088</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1231</v>
+        <v>1200</v>
       </c>
       <c r="C6" t="n">
-        <v>3276</v>
+        <v>4569</v>
       </c>
       <c r="D6" t="n">
-        <v>1388</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>592</v>
+        <v>557</v>
       </c>
       <c r="C7" t="n">
-        <v>1993</v>
+        <v>2491</v>
       </c>
       <c r="D7" t="n">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="C8" t="n">
-        <v>1248</v>
+        <v>1146</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>616</v>
+        <v>462</v>
       </c>
       <c r="D9" t="n">
         <v>264</v>
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>291</v>
+        <v>247</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
         <v>63</v>
@@ -2523,7 +2523,7 @@
         <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>34</v>
+      </c>
+      <c r="D16" t="n">
         <v>35</v>
-      </c>
-      <c r="D16" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3507</v>
+        <v>3524</v>
       </c>
       <c r="C2" t="n">
-        <v>3074</v>
+        <v>5887</v>
       </c>
       <c r="D2" t="n">
-        <v>16957</v>
+        <v>17532</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4818</v>
+        <v>5014</v>
       </c>
       <c r="C3" t="n">
-        <v>5023</v>
+        <v>7616</v>
       </c>
       <c r="D3" t="n">
-        <v>22129</v>
+        <v>20896</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4058</v>
+        <v>4111</v>
       </c>
       <c r="C4" t="n">
-        <v>6777</v>
+        <v>8360</v>
       </c>
       <c r="D4" t="n">
-        <v>14929</v>
+        <v>14378</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2122</v>
+        <v>2111</v>
       </c>
       <c r="C5" t="n">
-        <v>6818</v>
+        <v>8808</v>
       </c>
       <c r="D5" t="n">
-        <v>5301</v>
+        <v>5378</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1047</v>
+        <v>991</v>
       </c>
       <c r="C6" t="n">
-        <v>4005</v>
+        <v>5280</v>
       </c>
       <c r="D6" t="n">
-        <v>1353</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="C7" t="n">
-        <v>2159</v>
+        <v>2397</v>
       </c>
       <c r="D7" t="n">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>995</v>
+        <v>789</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>285</v>
+        <v>242</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -2820,7 +2820,7 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>33</v>
+      </c>
+      <c r="D15" t="n">
         <v>34</v>
-      </c>
-      <c r="D15" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3892</v>
+        <v>4611</v>
       </c>
       <c r="C2" t="n">
-        <v>4361</v>
+        <v>6910</v>
       </c>
       <c r="D2" t="n">
-        <v>18195</v>
+        <v>18258</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3654</v>
+        <v>3748</v>
       </c>
       <c r="C3" t="n">
-        <v>3640</v>
+        <v>6135</v>
       </c>
       <c r="D3" t="n">
-        <v>19938</v>
+        <v>19094</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3813</v>
+        <v>3935</v>
       </c>
       <c r="C4" t="n">
-        <v>5859</v>
+        <v>7850</v>
       </c>
       <c r="D4" t="n">
-        <v>15793</v>
+        <v>14942</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2577</v>
+        <v>2556</v>
       </c>
       <c r="C5" t="n">
-        <v>6723</v>
+        <v>8515</v>
       </c>
       <c r="D5" t="n">
-        <v>6526</v>
+        <v>6510</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1333</v>
+        <v>1262</v>
       </c>
       <c r="C6" t="n">
-        <v>5195</v>
+        <v>6707</v>
       </c>
       <c r="D6" t="n">
-        <v>1866</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>395</v>
+        <v>363</v>
       </c>
       <c r="C7" t="n">
-        <v>2942</v>
+        <v>3544</v>
       </c>
       <c r="D7" t="n">
-        <v>679</v>
+        <v>669</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>1436</v>
+        <v>1355</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>522</v>
+        <v>415</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3047</v>
+        <v>3188</v>
       </c>
       <c r="C2" t="n">
-        <v>3023</v>
+        <v>3691</v>
       </c>
       <c r="D2" t="n">
-        <v>13315</v>
+        <v>14843</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3269</v>
+        <v>3516</v>
       </c>
       <c r="C3" t="n">
-        <v>3561</v>
+        <v>5910</v>
       </c>
       <c r="D3" t="n">
-        <v>18644</v>
+        <v>17992</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3435</v>
+        <v>3542</v>
       </c>
       <c r="C4" t="n">
-        <v>4989</v>
+        <v>7254</v>
       </c>
       <c r="D4" t="n">
-        <v>16021</v>
+        <v>15149</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2818</v>
+        <v>2806</v>
       </c>
       <c r="C5" t="n">
-        <v>6526</v>
+        <v>8359</v>
       </c>
       <c r="D5" t="n">
-        <v>7520</v>
+        <v>7327</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1558</v>
+        <v>1459</v>
       </c>
       <c r="C6" t="n">
-        <v>5883</v>
+        <v>7513</v>
       </c>
       <c r="D6" t="n">
-        <v>2282</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>368</v>
+        <v>321</v>
       </c>
       <c r="C7" t="n">
-        <v>3694</v>
+        <v>4498</v>
       </c>
       <c r="D7" t="n">
-        <v>780</v>
+        <v>755</v>
       </c>
     </row>
     <row r="8">
@@ -3352,10 +3352,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>1818</v>
+        <v>1798</v>
       </c>
       <c r="D8" t="n">
         <v>411</v>
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>608</v>
+        <v>468</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
         <v>178</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3428,7 +3428,7 @@
         <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5490</v>
+        <v>5552</v>
       </c>
       <c r="C2" t="n">
-        <v>4183</v>
+        <v>5267</v>
       </c>
       <c r="D2" t="n">
-        <v>19903</v>
+        <v>21083</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2684</v>
+        <v>2869</v>
       </c>
       <c r="C3" t="n">
-        <v>3002</v>
+        <v>4530</v>
       </c>
       <c r="D3" t="n">
-        <v>16811</v>
+        <v>16516</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2934</v>
+        <v>3070</v>
       </c>
       <c r="C4" t="n">
-        <v>4234</v>
+        <v>6561</v>
       </c>
       <c r="D4" t="n">
-        <v>15911</v>
+        <v>15070</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2791</v>
+        <v>2806</v>
       </c>
       <c r="C5" t="n">
-        <v>5755</v>
+        <v>7760</v>
       </c>
       <c r="D5" t="n">
-        <v>8433</v>
+        <v>8010</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1829</v>
+        <v>1736</v>
       </c>
       <c r="C6" t="n">
-        <v>6143</v>
+        <v>7761</v>
       </c>
       <c r="D6" t="n">
-        <v>2884</v>
+        <v>2892</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>672</v>
+        <v>592</v>
       </c>
       <c r="C7" t="n">
-        <v>4507</v>
+        <v>5559</v>
       </c>
       <c r="D7" t="n">
-        <v>963</v>
+        <v>928</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>2479</v>
+        <v>2714</v>
       </c>
       <c r="D8" t="n">
-        <v>450</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1016</v>
+        <v>871</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>341</v>
+        <v>284</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8119</v>
+        <v>7244</v>
       </c>
       <c r="C2" t="n">
-        <v>5571</v>
+        <v>2641</v>
       </c>
       <c r="D2" t="n">
-        <v>7197</v>
+        <v>7893</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3927</v>
+        <v>4056</v>
       </c>
       <c r="C2" t="n">
-        <v>2375</v>
+        <v>3118</v>
       </c>
       <c r="D2" t="n">
-        <v>14649</v>
+        <v>15686</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3694</v>
+        <v>3864</v>
       </c>
       <c r="C3" t="n">
-        <v>3535</v>
+        <v>5159</v>
       </c>
       <c r="D3" t="n">
-        <v>18481</v>
+        <v>18193</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4076</v>
+        <v>4162</v>
       </c>
       <c r="C4" t="n">
-        <v>6149</v>
+        <v>9190</v>
       </c>
       <c r="D4" t="n">
-        <v>16148</v>
+        <v>15232</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1767</v>
+        <v>1629</v>
       </c>
       <c r="C5" t="n">
-        <v>8572</v>
+        <v>11078</v>
       </c>
       <c r="D5" t="n">
-        <v>7565</v>
+        <v>7212</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>620</v>
+        <v>547</v>
       </c>
       <c r="C6" t="n">
-        <v>5620</v>
+        <v>6816</v>
       </c>
       <c r="D6" t="n">
-        <v>2234</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>2429</v>
+        <v>2659</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>995</v>
+        <v>853</v>
       </c>
       <c r="D8" t="n">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>334</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8127</v>
+        <v>7626</v>
       </c>
       <c r="C2" t="n">
-        <v>6656</v>
+        <v>3344</v>
       </c>
       <c r="D2" t="n">
-        <v>14546</v>
+        <v>27993</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3448</v>
+        <v>3077</v>
       </c>
       <c r="C3" t="n">
-        <v>2807</v>
+        <v>1352</v>
       </c>
       <c r="D3" t="n">
-        <v>1848</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="4">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6096</v>
+        <v>6939</v>
       </c>
       <c r="C2" t="n">
-        <v>4897</v>
+        <v>8316</v>
       </c>
       <c r="D2" t="n">
-        <v>26720</v>
+        <v>28103</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4755</v>
+        <v>4395</v>
       </c>
       <c r="C3" t="n">
-        <v>4299</v>
+        <v>2138</v>
       </c>
       <c r="D3" t="n">
-        <v>3845</v>
+        <v>6193</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1531</v>
+        <v>1371</v>
       </c>
       <c r="C4" t="n">
-        <v>1687</v>
+        <v>836</v>
       </c>
       <c r="D4" t="n">
-        <v>1553</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5613</v>
+        <v>6643</v>
       </c>
       <c r="C2" t="n">
-        <v>3034</v>
+        <v>8928</v>
       </c>
       <c r="D2" t="n">
-        <v>30447</v>
+        <v>25056</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4455</v>
+        <v>4629</v>
       </c>
       <c r="C3" t="n">
-        <v>4003</v>
+        <v>4766</v>
       </c>
       <c r="D3" t="n">
-        <v>7228</v>
+        <v>9252</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2676</v>
+        <v>2442</v>
       </c>
       <c r="C4" t="n">
-        <v>3131</v>
+        <v>1556</v>
       </c>
       <c r="D4" t="n">
-        <v>1945</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>675</v>
+        <v>622</v>
       </c>
       <c r="C5" t="n">
-        <v>1018</v>
+        <v>552</v>
       </c>
       <c r="D5" t="n">
-        <v>1205</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="D6" t="n">
         <v>910</v>
@@ -5207,10 +5207,10 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>631</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5249,7 +5249,7 @@
         <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5319,7 +5319,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6507</v>
+        <v>6040</v>
       </c>
       <c r="C2" t="n">
-        <v>4024</v>
+        <v>7215</v>
       </c>
       <c r="D2" t="n">
-        <v>31688</v>
+        <v>25189</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4122</v>
+        <v>4588</v>
       </c>
       <c r="C3" t="n">
-        <v>3050</v>
+        <v>6012</v>
       </c>
       <c r="D3" t="n">
-        <v>10248</v>
+        <v>11002</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3037</v>
+        <v>2997</v>
       </c>
       <c r="C4" t="n">
-        <v>3534</v>
+        <v>3249</v>
       </c>
       <c r="D4" t="n">
-        <v>2849</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1375</v>
+        <v>1258</v>
       </c>
       <c r="C5" t="n">
-        <v>2082</v>
+        <v>1055</v>
       </c>
       <c r="D5" t="n">
-        <v>1284</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>353</v>
+        <v>332</v>
       </c>
       <c r="C6" t="n">
-        <v>664</v>
+        <v>424</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5549,7 +5549,7 @@
         <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
         <v>187</v>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6823</v>
+        <v>7469</v>
       </c>
       <c r="C2" t="n">
-        <v>5582</v>
+        <v>14292</v>
       </c>
       <c r="D2" t="n">
-        <v>30679</v>
+        <v>38673</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3837</v>
+        <v>3856</v>
       </c>
       <c r="C3" t="n">
-        <v>2906</v>
+        <v>5428</v>
       </c>
       <c r="D3" t="n">
-        <v>12028</v>
+        <v>11651</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2209</v>
+        <v>2338</v>
       </c>
       <c r="C4" t="n">
-        <v>2675</v>
+        <v>3885</v>
       </c>
       <c r="D4" t="n">
-        <v>3590</v>
+        <v>4215</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1158</v>
+        <v>1111</v>
       </c>
       <c r="C5" t="n">
-        <v>2056</v>
+        <v>1623</v>
       </c>
       <c r="D5" t="n">
-        <v>1217</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>404</v>
+        <v>372</v>
       </c>
       <c r="C6" t="n">
-        <v>928</v>
+        <v>500</v>
       </c>
       <c r="D6" t="n">
-        <v>765</v>
+        <v>776</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>321</v>
+        <v>246</v>
       </c>
       <c r="D7" t="n">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5916,7 +5916,7 @@
         <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7228</v>
+        <v>6914</v>
       </c>
       <c r="C2" t="n">
-        <v>8200</v>
+        <v>6301</v>
       </c>
       <c r="D2" t="n">
-        <v>37875</v>
+        <v>33004</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4429</v>
+        <v>4743</v>
       </c>
       <c r="C3" t="n">
-        <v>3862</v>
+        <v>9131</v>
       </c>
       <c r="D3" t="n">
-        <v>14521</v>
+        <v>15333</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2654</v>
+        <v>2684</v>
       </c>
       <c r="C4" t="n">
-        <v>2761</v>
+        <v>4737</v>
       </c>
       <c r="D4" t="n">
-        <v>5147</v>
+        <v>5545</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1494</v>
+        <v>1539</v>
       </c>
       <c r="C5" t="n">
-        <v>2381</v>
+        <v>2913</v>
       </c>
       <c r="D5" t="n">
-        <v>1658</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>729</v>
+        <v>681</v>
       </c>
       <c r="C6" t="n">
-        <v>1566</v>
+        <v>1129</v>
       </c>
       <c r="D6" t="n">
-        <v>833</v>
+        <v>879</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="C7" t="n">
-        <v>665</v>
+        <v>385</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>276</v>
+        <v>235</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
         <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6227,7 +6227,7 @@
         <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>64</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5941</v>
+        <v>6241</v>
       </c>
       <c r="C2" t="n">
-        <v>6048</v>
+        <v>4723</v>
       </c>
       <c r="D2" t="n">
-        <v>33248</v>
+        <v>37095</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4757</v>
+        <v>4771</v>
       </c>
       <c r="C3" t="n">
-        <v>5390</v>
+        <v>6605</v>
       </c>
       <c r="D3" t="n">
-        <v>17212</v>
+        <v>17056</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3024</v>
+        <v>3192</v>
       </c>
       <c r="C4" t="n">
-        <v>3327</v>
+        <v>7039</v>
       </c>
       <c r="D4" t="n">
-        <v>6790</v>
+        <v>7255</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1830</v>
+        <v>1842</v>
       </c>
       <c r="C5" t="n">
-        <v>2516</v>
+        <v>3850</v>
       </c>
       <c r="D5" t="n">
-        <v>2228</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C6" t="n">
-        <v>1985</v>
+        <v>2058</v>
       </c>
       <c r="D6" t="n">
-        <v>971</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>425</v>
+        <v>390</v>
       </c>
       <c r="C7" t="n">
-        <v>1141</v>
+        <v>771</v>
       </c>
       <c r="D7" t="n">
-        <v>596</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>474</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
         <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -6633,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_43_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_43_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6847</v>
+        <v>5611</v>
       </c>
       <c r="C2" t="n">
-        <v>7177</v>
+        <v>4478</v>
       </c>
       <c r="D2" t="n">
-        <v>41815</v>
+        <v>23870</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4523</v>
+        <v>3800</v>
       </c>
       <c r="C3" t="n">
-        <v>4982</v>
+        <v>2923</v>
       </c>
       <c r="D3" t="n">
-        <v>18768</v>
+        <v>15836</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3338</v>
+        <v>2723</v>
       </c>
       <c r="C4" t="n">
-        <v>6604</v>
+        <v>3061</v>
       </c>
       <c r="D4" t="n">
-        <v>8658</v>
+        <v>7983</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2156</v>
+        <v>1779</v>
       </c>
       <c r="C5" t="n">
-        <v>5361</v>
+        <v>3031</v>
       </c>
       <c r="D5" t="n">
-        <v>3239</v>
+        <v>2957</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1272</v>
+        <v>1053</v>
       </c>
       <c r="C6" t="n">
-        <v>2876</v>
+        <v>2267</v>
       </c>
       <c r="D6" t="n">
-        <v>1273</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="7">
@@ -850,10 +850,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>591</v>
+        <v>513</v>
       </c>
       <c r="C7" t="n">
-        <v>1388</v>
+        <v>1294</v>
       </c>
       <c r="D7" t="n">
         <v>661</v>
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="C8" t="n">
-        <v>520</v>
+        <v>585</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>257</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
         <v>307</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9356</v>
+        <v>6782</v>
       </c>
       <c r="C2" t="n">
-        <v>11572</v>
+        <v>8655</v>
       </c>
       <c r="D2" t="n">
-        <v>38523</v>
+        <v>25594</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4557</v>
+        <v>3788</v>
       </c>
       <c r="C3" t="n">
-        <v>5252</v>
+        <v>3217</v>
       </c>
       <c r="D3" t="n">
-        <v>20821</v>
+        <v>15903</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3276</v>
+        <v>2770</v>
       </c>
       <c r="C4" t="n">
-        <v>5703</v>
+        <v>2927</v>
       </c>
       <c r="D4" t="n">
-        <v>9864</v>
+        <v>9097</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2344</v>
+        <v>1944</v>
       </c>
       <c r="C5" t="n">
-        <v>5758</v>
+        <v>2982</v>
       </c>
       <c r="D5" t="n">
-        <v>3972</v>
+        <v>3658</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1497</v>
+        <v>1257</v>
       </c>
       <c r="C6" t="n">
-        <v>3945</v>
+        <v>2581</v>
       </c>
       <c r="D6" t="n">
-        <v>1526</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>789</v>
+        <v>683</v>
       </c>
       <c r="C7" t="n">
-        <v>2015</v>
+        <v>1751</v>
       </c>
       <c r="D7" t="n">
-        <v>744</v>
+        <v>730</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>321</v>
+        <v>292</v>
       </c>
       <c r="C8" t="n">
-        <v>885</v>
+        <v>898</v>
       </c>
       <c r="D8" t="n">
-        <v>455</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C9" t="n">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9530</v>
+        <v>8665</v>
       </c>
       <c r="C2" t="n">
-        <v>11231</v>
+        <v>9496</v>
       </c>
       <c r="D2" t="n">
-        <v>34956</v>
+        <v>23663</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5215</v>
+        <v>4128</v>
       </c>
       <c r="C3" t="n">
-        <v>6896</v>
+        <v>4967</v>
       </c>
       <c r="D3" t="n">
-        <v>21612</v>
+        <v>16152</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3250</v>
+        <v>2762</v>
       </c>
       <c r="C4" t="n">
-        <v>5339</v>
+        <v>3002</v>
       </c>
       <c r="D4" t="n">
-        <v>11047</v>
+        <v>9931</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2406</v>
+        <v>2034</v>
       </c>
       <c r="C5" t="n">
-        <v>5615</v>
+        <v>2866</v>
       </c>
       <c r="D5" t="n">
-        <v>4699</v>
+        <v>4347</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1663</v>
+        <v>1414</v>
       </c>
       <c r="C6" t="n">
-        <v>4586</v>
+        <v>2733</v>
       </c>
       <c r="D6" t="n">
-        <v>1819</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>952</v>
+        <v>839</v>
       </c>
       <c r="C7" t="n">
-        <v>2751</v>
+        <v>2091</v>
       </c>
       <c r="D7" t="n">
-        <v>843</v>
+        <v>822</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>437</v>
+        <v>398</v>
       </c>
       <c r="C8" t="n">
-        <v>1316</v>
+        <v>1257</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>501</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C9" t="n">
-        <v>546</v>
+        <v>606</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>269</v>
+        <v>307</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D11" t="n">
         <v>208</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8834</v>
+        <v>7751</v>
       </c>
       <c r="C2" t="n">
-        <v>7816</v>
+        <v>6229</v>
       </c>
       <c r="D2" t="n">
-        <v>29002</v>
+        <v>19206</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6012</v>
+        <v>5061</v>
       </c>
       <c r="C3" t="n">
-        <v>10043</v>
+        <v>7259</v>
       </c>
       <c r="D3" t="n">
-        <v>23103</v>
+        <v>18090</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2223</v>
+        <v>1879</v>
       </c>
       <c r="C4" t="n">
-        <v>8260</v>
+        <v>4509</v>
       </c>
       <c r="D4" t="n">
-        <v>10459</v>
+        <v>9636</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1536</v>
+        <v>1306</v>
       </c>
       <c r="C5" t="n">
-        <v>4494</v>
+        <v>2678</v>
       </c>
       <c r="D5" t="n">
-        <v>3045</v>
+        <v>2952</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>879</v>
+        <v>775</v>
       </c>
       <c r="C6" t="n">
-        <v>2695</v>
+        <v>2049</v>
       </c>
       <c r="D6" t="n">
-        <v>826</v>
+        <v>805</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>403</v>
+        <v>367</v>
       </c>
       <c r="C7" t="n">
-        <v>1289</v>
+        <v>1231</v>
       </c>
       <c r="D7" t="n">
-        <v>472</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C8" t="n">
-        <v>535</v>
+        <v>593</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>263</v>
+        <v>300</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="D10" t="n">
         <v>203</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
         <v>98</v>
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5537</v>
+        <v>4586</v>
       </c>
       <c r="C2" t="n">
-        <v>4428</v>
+        <v>2767</v>
       </c>
       <c r="D2" t="n">
-        <v>20332</v>
+        <v>14210</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6188</v>
+        <v>5363</v>
       </c>
       <c r="C3" t="n">
-        <v>8236</v>
+        <v>6105</v>
       </c>
       <c r="D3" t="n">
-        <v>22796</v>
+        <v>17353</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3129</v>
+        <v>2720</v>
       </c>
       <c r="C4" t="n">
-        <v>9130</v>
+        <v>5934</v>
       </c>
       <c r="D4" t="n">
-        <v>12062</v>
+        <v>10734</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1689</v>
+        <v>1457</v>
       </c>
       <c r="C5" t="n">
-        <v>6134</v>
+        <v>3541</v>
       </c>
       <c r="D5" t="n">
-        <v>3965</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1041</v>
+        <v>920</v>
       </c>
       <c r="C6" t="n">
-        <v>3437</v>
+        <v>2382</v>
       </c>
       <c r="D6" t="n">
-        <v>1032</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="C7" t="n">
-        <v>1774</v>
+        <v>1579</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8" t="n">
-        <v>731</v>
+        <v>790</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>364</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5780</v>
+        <v>4574</v>
       </c>
       <c r="C2" t="n">
-        <v>12225</v>
+        <v>5640</v>
       </c>
       <c r="D2" t="n">
-        <v>25124</v>
+        <v>18739</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5023</v>
+        <v>4209</v>
       </c>
       <c r="C3" t="n">
-        <v>5759</v>
+        <v>3913</v>
       </c>
       <c r="D3" t="n">
-        <v>20929</v>
+        <v>15820</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3761</v>
+        <v>3377</v>
       </c>
       <c r="C4" t="n">
-        <v>8510</v>
+        <v>5899</v>
       </c>
       <c r="D4" t="n">
-        <v>13447</v>
+        <v>11551</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2027</v>
+        <v>1784</v>
       </c>
       <c r="C5" t="n">
-        <v>7445</v>
+        <v>4695</v>
       </c>
       <c r="D5" t="n">
-        <v>5088</v>
+        <v>4829</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1200</v>
+        <v>1064</v>
       </c>
       <c r="C6" t="n">
-        <v>4569</v>
+        <v>2902</v>
       </c>
       <c r="D6" t="n">
-        <v>1440</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>557</v>
+        <v>525</v>
       </c>
       <c r="C7" t="n">
-        <v>2491</v>
+        <v>1963</v>
       </c>
       <c r="D7" t="n">
-        <v>580</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C8" t="n">
-        <v>1146</v>
+        <v>1137</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>462</v>
+        <v>542</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10">
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="D10" t="n">
         <v>213</v>
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2565,7 +2565,7 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3524</v>
+        <v>2646</v>
       </c>
       <c r="C2" t="n">
-        <v>5887</v>
+        <v>2501</v>
       </c>
       <c r="D2" t="n">
-        <v>17532</v>
+        <v>12921</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5014</v>
+        <v>4183</v>
       </c>
       <c r="C3" t="n">
-        <v>7616</v>
+        <v>4359</v>
       </c>
       <c r="D3" t="n">
-        <v>20896</v>
+        <v>15767</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4111</v>
+        <v>3747</v>
       </c>
       <c r="C4" t="n">
-        <v>8360</v>
+        <v>5674</v>
       </c>
       <c r="D4" t="n">
-        <v>14378</v>
+        <v>12164</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2111</v>
+        <v>1882</v>
       </c>
       <c r="C5" t="n">
-        <v>8808</v>
+        <v>5574</v>
       </c>
       <c r="D5" t="n">
-        <v>5378</v>
+        <v>5222</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>991</v>
+        <v>937</v>
       </c>
       <c r="C6" t="n">
-        <v>5280</v>
+        <v>3750</v>
       </c>
       <c r="D6" t="n">
-        <v>1398</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="7">
@@ -2719,10 +2719,10 @@
         <v>170</v>
       </c>
       <c r="C7" t="n">
-        <v>2397</v>
+        <v>2101</v>
       </c>
       <c r="D7" t="n">
-        <v>579</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>789</v>
+        <v>910</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>48</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2862,7 +2862,7 @@
         <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4611</v>
+        <v>4325</v>
       </c>
       <c r="C2" t="n">
-        <v>6910</v>
+        <v>1925</v>
       </c>
       <c r="D2" t="n">
-        <v>18258</v>
+        <v>17656</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3748</v>
+        <v>2998</v>
       </c>
       <c r="C3" t="n">
-        <v>6135</v>
+        <v>3069</v>
       </c>
       <c r="D3" t="n">
-        <v>19094</v>
+        <v>14272</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3935</v>
+        <v>3476</v>
       </c>
       <c r="C4" t="n">
-        <v>7850</v>
+        <v>4899</v>
       </c>
       <c r="D4" t="n">
-        <v>14942</v>
+        <v>12533</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2556</v>
+        <v>2360</v>
       </c>
       <c r="C5" t="n">
-        <v>8515</v>
+        <v>5559</v>
       </c>
       <c r="D5" t="n">
-        <v>6510</v>
+        <v>6129</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1262</v>
+        <v>1205</v>
       </c>
       <c r="C6" t="n">
-        <v>6707</v>
+        <v>4609</v>
       </c>
       <c r="D6" t="n">
-        <v>1928</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C7" t="n">
-        <v>3544</v>
+        <v>2815</v>
       </c>
       <c r="D7" t="n">
-        <v>669</v>
+        <v>718</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>1355</v>
+        <v>1403</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>415</v>
+        <v>495</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3188</v>
+        <v>3086</v>
       </c>
       <c r="C2" t="n">
-        <v>3691</v>
+        <v>2353</v>
       </c>
       <c r="D2" t="n">
-        <v>14843</v>
+        <v>12835</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3516</v>
+        <v>3026</v>
       </c>
       <c r="C3" t="n">
-        <v>5910</v>
+        <v>2330</v>
       </c>
       <c r="D3" t="n">
-        <v>17992</v>
+        <v>13905</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3542</v>
+        <v>3064</v>
       </c>
       <c r="C4" t="n">
-        <v>7254</v>
+        <v>4130</v>
       </c>
       <c r="D4" t="n">
-        <v>15149</v>
+        <v>12522</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2806</v>
+        <v>2593</v>
       </c>
       <c r="C5" t="n">
-        <v>8359</v>
+        <v>5397</v>
       </c>
       <c r="D5" t="n">
-        <v>7327</v>
+        <v>6859</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1459</v>
+        <v>1427</v>
       </c>
       <c r="C6" t="n">
-        <v>7513</v>
+        <v>5119</v>
       </c>
       <c r="D6" t="n">
-        <v>2294</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>321</v>
+        <v>372</v>
       </c>
       <c r="C7" t="n">
-        <v>4498</v>
+        <v>3499</v>
       </c>
       <c r="D7" t="n">
-        <v>755</v>
+        <v>831</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
         <v>1798</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>468</v>
+        <v>625</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5552</v>
+        <v>4324</v>
       </c>
       <c r="C2" t="n">
-        <v>5267</v>
+        <v>5754</v>
       </c>
       <c r="D2" t="n">
-        <v>21083</v>
+        <v>15158</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2869</v>
+        <v>2560</v>
       </c>
       <c r="C3" t="n">
-        <v>4530</v>
+        <v>2066</v>
       </c>
       <c r="D3" t="n">
-        <v>16516</v>
+        <v>12855</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3070</v>
+        <v>2676</v>
       </c>
       <c r="C4" t="n">
-        <v>6561</v>
+        <v>3214</v>
       </c>
       <c r="D4" t="n">
-        <v>15070</v>
+        <v>12353</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2806</v>
+        <v>2521</v>
       </c>
       <c r="C5" t="n">
-        <v>7760</v>
+        <v>4777</v>
       </c>
       <c r="D5" t="n">
-        <v>8010</v>
+        <v>7465</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1736</v>
+        <v>1724</v>
       </c>
       <c r="C6" t="n">
-        <v>7761</v>
+        <v>5187</v>
       </c>
       <c r="D6" t="n">
-        <v>2892</v>
+        <v>2918</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>592</v>
+        <v>656</v>
       </c>
       <c r="C7" t="n">
-        <v>5559</v>
+        <v>4148</v>
       </c>
       <c r="D7" t="n">
-        <v>928</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="C8" t="n">
-        <v>2714</v>
+        <v>2465</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>871</v>
+        <v>1044</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>284</v>
+        <v>361</v>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7244</v>
+        <v>5873</v>
       </c>
       <c r="C2" t="n">
-        <v>2641</v>
+        <v>3318</v>
       </c>
       <c r="D2" t="n">
-        <v>7893</v>
+        <v>7969</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4056</v>
+        <v>2993</v>
       </c>
       <c r="C2" t="n">
-        <v>3118</v>
+        <v>3131</v>
       </c>
       <c r="D2" t="n">
-        <v>15686</v>
+        <v>11035</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3864</v>
+        <v>3463</v>
       </c>
       <c r="C3" t="n">
-        <v>5159</v>
+        <v>3178</v>
       </c>
       <c r="D3" t="n">
-        <v>18193</v>
+        <v>14143</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4162</v>
+        <v>3671</v>
       </c>
       <c r="C4" t="n">
-        <v>9190</v>
+        <v>4693</v>
       </c>
       <c r="D4" t="n">
-        <v>15232</v>
+        <v>12867</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1629</v>
+        <v>1732</v>
       </c>
       <c r="C5" t="n">
-        <v>11078</v>
+        <v>7170</v>
       </c>
       <c r="D5" t="n">
-        <v>7212</v>
+        <v>6847</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>547</v>
+        <v>606</v>
       </c>
       <c r="C6" t="n">
-        <v>6816</v>
+        <v>5234</v>
       </c>
       <c r="D6" t="n">
-        <v>2189</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
-        <v>2659</v>
+        <v>2415</v>
       </c>
       <c r="D7" t="n">
-        <v>543</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>853</v>
+        <v>1023</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>278</v>
+        <v>353</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7626</v>
+        <v>6687</v>
       </c>
       <c r="C2" t="n">
-        <v>3344</v>
+        <v>3583</v>
       </c>
       <c r="D2" t="n">
-        <v>27993</v>
+        <v>18176</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3077</v>
+        <v>2495</v>
       </c>
       <c r="C3" t="n">
-        <v>1352</v>
+        <v>1698</v>
       </c>
       <c r="D3" t="n">
-        <v>1965</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6939</v>
+        <v>4995</v>
       </c>
       <c r="C2" t="n">
-        <v>8316</v>
+        <v>6370</v>
       </c>
       <c r="D2" t="n">
-        <v>28103</v>
+        <v>21401</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4395</v>
+        <v>3769</v>
       </c>
       <c r="C3" t="n">
-        <v>2138</v>
+        <v>2396</v>
       </c>
       <c r="D3" t="n">
-        <v>6193</v>
+        <v>4601</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1371</v>
+        <v>1117</v>
       </c>
       <c r="C4" t="n">
-        <v>836</v>
+        <v>1054</v>
       </c>
       <c r="D4" t="n">
-        <v>1577</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
         <v>411</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6643</v>
+        <v>5111</v>
       </c>
       <c r="C2" t="n">
-        <v>8928</v>
+        <v>4666</v>
       </c>
       <c r="D2" t="n">
-        <v>25056</v>
+        <v>23936</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4629</v>
+        <v>3595</v>
       </c>
       <c r="C3" t="n">
-        <v>4766</v>
+        <v>3949</v>
       </c>
       <c r="D3" t="n">
-        <v>9252</v>
+        <v>6957</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2442</v>
+        <v>2068</v>
       </c>
       <c r="C4" t="n">
-        <v>1556</v>
+        <v>1782</v>
       </c>
       <c r="D4" t="n">
-        <v>2415</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>622</v>
+        <v>519</v>
       </c>
       <c r="C5" t="n">
-        <v>552</v>
+        <v>679</v>
       </c>
       <c r="D5" t="n">
-        <v>1209</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
         <v>910</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
         <v>372</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
         <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5361,7 +5361,7 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6040</v>
+        <v>5087</v>
       </c>
       <c r="C2" t="n">
-        <v>7215</v>
+        <v>5501</v>
       </c>
       <c r="D2" t="n">
-        <v>25189</v>
+        <v>31787</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4588</v>
+        <v>3545</v>
       </c>
       <c r="C3" t="n">
-        <v>6012</v>
+        <v>3757</v>
       </c>
       <c r="D3" t="n">
-        <v>11002</v>
+        <v>9048</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2997</v>
+        <v>2391</v>
       </c>
       <c r="C4" t="n">
-        <v>3249</v>
+        <v>2930</v>
       </c>
       <c r="D4" t="n">
-        <v>3588</v>
+        <v>2918</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1258</v>
+        <v>1079</v>
       </c>
       <c r="C5" t="n">
-        <v>1055</v>
+        <v>1247</v>
       </c>
       <c r="D5" t="n">
-        <v>1369</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>332</v>
+        <v>287</v>
       </c>
       <c r="C6" t="n">
-        <v>424</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
         <v>949</v>
@@ -5515,7 +5515,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
         <v>484</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
         <v>378</v>
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7469</v>
+        <v>5679</v>
       </c>
       <c r="C2" t="n">
-        <v>14292</v>
+        <v>4165</v>
       </c>
       <c r="D2" t="n">
-        <v>38673</v>
+        <v>33216</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3856</v>
+        <v>3140</v>
       </c>
       <c r="C3" t="n">
-        <v>5428</v>
+        <v>3819</v>
       </c>
       <c r="D3" t="n">
-        <v>11651</v>
+        <v>11164</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2338</v>
+        <v>1854</v>
       </c>
       <c r="C4" t="n">
-        <v>3885</v>
+        <v>2783</v>
       </c>
       <c r="D4" t="n">
-        <v>4215</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1111</v>
+        <v>904</v>
       </c>
       <c r="C5" t="n">
-        <v>1623</v>
+        <v>1555</v>
       </c>
       <c r="D5" t="n">
-        <v>1375</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>372</v>
+        <v>324</v>
       </c>
       <c r="C6" t="n">
-        <v>500</v>
+        <v>591</v>
       </c>
       <c r="D6" t="n">
-        <v>776</v>
+        <v>765</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6914</v>
+        <v>5828</v>
       </c>
       <c r="C2" t="n">
-        <v>6301</v>
+        <v>3395</v>
       </c>
       <c r="D2" t="n">
-        <v>33004</v>
+        <v>29903</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4743</v>
+        <v>3683</v>
       </c>
       <c r="C3" t="n">
-        <v>9131</v>
+        <v>3448</v>
       </c>
       <c r="D3" t="n">
-        <v>15333</v>
+        <v>14205</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2684</v>
+        <v>2202</v>
       </c>
       <c r="C4" t="n">
-        <v>4737</v>
+        <v>3371</v>
       </c>
       <c r="D4" t="n">
-        <v>5545</v>
+        <v>4951</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1539</v>
+        <v>1239</v>
       </c>
       <c r="C5" t="n">
-        <v>2913</v>
+        <v>2265</v>
       </c>
       <c r="D5" t="n">
-        <v>1905</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>681</v>
+        <v>570</v>
       </c>
       <c r="C6" t="n">
-        <v>1129</v>
+        <v>1148</v>
       </c>
       <c r="D6" t="n">
-        <v>879</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="C7" t="n">
-        <v>385</v>
+        <v>455</v>
       </c>
       <c r="D7" t="n">
-        <v>551</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
         <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
         <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6241</v>
+        <v>5425</v>
       </c>
       <c r="C2" t="n">
-        <v>4723</v>
+        <v>3713</v>
       </c>
       <c r="D2" t="n">
-        <v>37095</v>
+        <v>22680</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4771</v>
+        <v>3900</v>
       </c>
       <c r="C3" t="n">
-        <v>6605</v>
+        <v>2980</v>
       </c>
       <c r="D3" t="n">
-        <v>17056</v>
+        <v>15933</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3192</v>
+        <v>2525</v>
       </c>
       <c r="C4" t="n">
-        <v>7039</v>
+        <v>3312</v>
       </c>
       <c r="D4" t="n">
-        <v>7255</v>
+        <v>6529</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1842</v>
+        <v>1526</v>
       </c>
       <c r="C5" t="n">
-        <v>3850</v>
+        <v>2844</v>
       </c>
       <c r="D5" t="n">
-        <v>2492</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1006</v>
+        <v>822</v>
       </c>
       <c r="C6" t="n">
-        <v>2058</v>
+        <v>1745</v>
       </c>
       <c r="D6" t="n">
-        <v>1053</v>
+        <v>985</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>390</v>
+        <v>342</v>
       </c>
       <c r="C7" t="n">
-        <v>771</v>
+        <v>828</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>352</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_43_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_43_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5611</v>
+        <v>1397</v>
       </c>
       <c r="C2" t="n">
-        <v>4478</v>
+        <v>3101</v>
       </c>
       <c r="D2" t="n">
-        <v>23870</v>
+        <v>19937</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3800</v>
+        <v>2017</v>
       </c>
       <c r="C3" t="n">
-        <v>2923</v>
+        <v>6365</v>
       </c>
       <c r="D3" t="n">
-        <v>15836</v>
+        <v>16483</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2723</v>
+        <v>1172</v>
       </c>
       <c r="C4" t="n">
-        <v>3061</v>
+        <v>5636</v>
       </c>
       <c r="D4" t="n">
-        <v>7983</v>
+        <v>6822</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1779</v>
+        <v>574</v>
       </c>
       <c r="C5" t="n">
-        <v>3031</v>
+        <v>3129</v>
       </c>
       <c r="D5" t="n">
-        <v>2957</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1053</v>
+        <v>250</v>
       </c>
       <c r="C6" t="n">
-        <v>2267</v>
+        <v>1446</v>
       </c>
       <c r="D6" t="n">
-        <v>1188</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>513</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>1294</v>
+        <v>621</v>
       </c>
       <c r="D7" t="n">
-        <v>661</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>193</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>585</v>
+        <v>345</v>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6782</v>
+        <v>1552</v>
       </c>
       <c r="C2" t="n">
-        <v>8655</v>
+        <v>8691</v>
       </c>
       <c r="D2" t="n">
-        <v>25594</v>
+        <v>21732</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3788</v>
+        <v>1441</v>
       </c>
       <c r="C3" t="n">
-        <v>3217</v>
+        <v>3968</v>
       </c>
       <c r="D3" t="n">
-        <v>15903</v>
+        <v>15848</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2770</v>
+        <v>1374</v>
       </c>
       <c r="C4" t="n">
-        <v>2927</v>
+        <v>5985</v>
       </c>
       <c r="D4" t="n">
-        <v>9097</v>
+        <v>8469</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1944</v>
+        <v>762</v>
       </c>
       <c r="C5" t="n">
-        <v>2982</v>
+        <v>4441</v>
       </c>
       <c r="D5" t="n">
-        <v>3658</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1257</v>
+        <v>360</v>
       </c>
       <c r="C6" t="n">
-        <v>2581</v>
+        <v>2300</v>
       </c>
       <c r="D6" t="n">
-        <v>1460</v>
+        <v>976</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>683</v>
+        <v>149</v>
       </c>
       <c r="C7" t="n">
-        <v>1751</v>
+        <v>1031</v>
       </c>
       <c r="D7" t="n">
-        <v>730</v>
+        <v>529</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>292</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>898</v>
+        <v>475</v>
       </c>
       <c r="D8" t="n">
-        <v>468</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>417</v>
+        <v>320</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8665</v>
+        <v>797</v>
       </c>
       <c r="C2" t="n">
-        <v>9496</v>
+        <v>3501</v>
       </c>
       <c r="D2" t="n">
-        <v>23663</v>
+        <v>14655</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4128</v>
+        <v>1429</v>
       </c>
       <c r="C3" t="n">
-        <v>4967</v>
+        <v>5685</v>
       </c>
       <c r="D3" t="n">
-        <v>16152</v>
+        <v>16170</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2762</v>
+        <v>1514</v>
       </c>
       <c r="C4" t="n">
-        <v>3002</v>
+        <v>5621</v>
       </c>
       <c r="D4" t="n">
-        <v>9931</v>
+        <v>9468</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2034</v>
+        <v>771</v>
       </c>
       <c r="C5" t="n">
-        <v>2866</v>
+        <v>5432</v>
       </c>
       <c r="D5" t="n">
-        <v>4347</v>
+        <v>3292</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1414</v>
+        <v>302</v>
       </c>
       <c r="C6" t="n">
-        <v>2733</v>
+        <v>3070</v>
       </c>
       <c r="D6" t="n">
-        <v>1778</v>
+        <v>984</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>839</v>
+        <v>75</v>
       </c>
       <c r="C7" t="n">
-        <v>2091</v>
+        <v>1036</v>
       </c>
       <c r="D7" t="n">
-        <v>822</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>398</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1257</v>
+        <v>490</v>
       </c>
       <c r="D8" t="n">
-        <v>501</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>158</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>606</v>
+        <v>243</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>307</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>261</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>201</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7751</v>
+        <v>743</v>
       </c>
       <c r="C2" t="n">
-        <v>6229</v>
+        <v>5464</v>
       </c>
       <c r="D2" t="n">
-        <v>19206</v>
+        <v>14766</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5061</v>
+        <v>969</v>
       </c>
       <c r="C3" t="n">
-        <v>7259</v>
+        <v>3943</v>
       </c>
       <c r="D3" t="n">
-        <v>18090</v>
+        <v>14801</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1879</v>
+        <v>1308</v>
       </c>
       <c r="C4" t="n">
-        <v>4509</v>
+        <v>5593</v>
       </c>
       <c r="D4" t="n">
-        <v>9636</v>
+        <v>10402</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1306</v>
+        <v>977</v>
       </c>
       <c r="C5" t="n">
-        <v>2678</v>
+        <v>5521</v>
       </c>
       <c r="D5" t="n">
-        <v>2952</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>775</v>
+        <v>453</v>
       </c>
       <c r="C6" t="n">
-        <v>2049</v>
+        <v>4201</v>
       </c>
       <c r="D6" t="n">
-        <v>805</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>367</v>
+        <v>140</v>
       </c>
       <c r="C7" t="n">
-        <v>1231</v>
+        <v>1992</v>
       </c>
       <c r="D7" t="n">
-        <v>490</v>
+        <v>623</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>145</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>593</v>
+        <v>734</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>300</v>
+        <v>342</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
+        <v>70</v>
+      </c>
+      <c r="D14" t="n">
         <v>69</v>
-      </c>
-      <c r="D14" t="n">
-        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4586</v>
+        <v>394</v>
       </c>
       <c r="C2" t="n">
-        <v>2767</v>
+        <v>2798</v>
       </c>
       <c r="D2" t="n">
-        <v>14210</v>
+        <v>10933</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5363</v>
+        <v>769</v>
       </c>
       <c r="C3" t="n">
-        <v>6105</v>
+        <v>4165</v>
       </c>
       <c r="D3" t="n">
-        <v>17353</v>
+        <v>14061</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2720</v>
+        <v>1096</v>
       </c>
       <c r="C4" t="n">
-        <v>5934</v>
+        <v>4845</v>
       </c>
       <c r="D4" t="n">
-        <v>10734</v>
+        <v>10861</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1457</v>
+        <v>1054</v>
       </c>
       <c r="C5" t="n">
-        <v>3541</v>
+        <v>5649</v>
       </c>
       <c r="D5" t="n">
-        <v>3817</v>
+        <v>5063</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>920</v>
+        <v>568</v>
       </c>
       <c r="C6" t="n">
-        <v>2382</v>
+        <v>4907</v>
       </c>
       <c r="D6" t="n">
-        <v>1045</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>358</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>1579</v>
+        <v>2798</v>
       </c>
       <c r="D7" t="n">
-        <v>540</v>
+        <v>700</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>790</v>
+        <v>1069</v>
       </c>
       <c r="D8" t="n">
-        <v>342</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>364</v>
+        <v>449</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4574</v>
+        <v>1291</v>
       </c>
       <c r="C2" t="n">
-        <v>5640</v>
+        <v>7885</v>
       </c>
       <c r="D2" t="n">
-        <v>18739</v>
+        <v>12660</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4209</v>
+        <v>515</v>
       </c>
       <c r="C3" t="n">
-        <v>3913</v>
+        <v>3083</v>
       </c>
       <c r="D3" t="n">
-        <v>15820</v>
+        <v>12778</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3377</v>
+        <v>835</v>
       </c>
       <c r="C4" t="n">
-        <v>5899</v>
+        <v>4404</v>
       </c>
       <c r="D4" t="n">
-        <v>11551</v>
+        <v>10948</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1784</v>
+        <v>987</v>
       </c>
       <c r="C5" t="n">
-        <v>4695</v>
+        <v>5199</v>
       </c>
       <c r="D5" t="n">
-        <v>4829</v>
+        <v>5855</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1064</v>
+        <v>706</v>
       </c>
       <c r="C6" t="n">
-        <v>2902</v>
+        <v>5193</v>
       </c>
       <c r="D6" t="n">
-        <v>1456</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>525</v>
+        <v>282</v>
       </c>
       <c r="C7" t="n">
-        <v>1963</v>
+        <v>3754</v>
       </c>
       <c r="D7" t="n">
-        <v>608</v>
+        <v>832</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>185</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>1137</v>
+        <v>1790</v>
       </c>
       <c r="D8" t="n">
-        <v>365</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>542</v>
+        <v>690</v>
       </c>
       <c r="D9" t="n">
-        <v>275</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>274</v>
+        <v>310</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>172</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2646</v>
+        <v>857</v>
       </c>
       <c r="C2" t="n">
-        <v>2501</v>
+        <v>4037</v>
       </c>
       <c r="D2" t="n">
-        <v>12921</v>
+        <v>9116</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4183</v>
+        <v>834</v>
       </c>
       <c r="C3" t="n">
-        <v>4359</v>
+        <v>4697</v>
       </c>
       <c r="D3" t="n">
-        <v>15767</v>
+        <v>13682</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3747</v>
+        <v>1320</v>
       </c>
       <c r="C4" t="n">
-        <v>5674</v>
+        <v>6008</v>
       </c>
       <c r="D4" t="n">
-        <v>12164</v>
+        <v>11343</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1882</v>
+        <v>734</v>
       </c>
       <c r="C5" t="n">
-        <v>5574</v>
+        <v>7458</v>
       </c>
       <c r="D5" t="n">
-        <v>5222</v>
+        <v>5395</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>937</v>
+        <v>260</v>
       </c>
       <c r="C6" t="n">
-        <v>3750</v>
+        <v>5052</v>
       </c>
       <c r="D6" t="n">
-        <v>1427</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="C7" t="n">
-        <v>2101</v>
+        <v>1754</v>
       </c>
       <c r="D7" t="n">
-        <v>606</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>910</v>
+        <v>676</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>168</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4325</v>
+        <v>441</v>
       </c>
       <c r="C2" t="n">
-        <v>1925</v>
+        <v>2529</v>
       </c>
       <c r="D2" t="n">
-        <v>17656</v>
+        <v>6923</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2998</v>
+        <v>708</v>
       </c>
       <c r="C3" t="n">
-        <v>3069</v>
+        <v>3840</v>
       </c>
       <c r="D3" t="n">
-        <v>14272</v>
+        <v>12043</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3476</v>
+        <v>917</v>
       </c>
       <c r="C4" t="n">
-        <v>4899</v>
+        <v>5056</v>
       </c>
       <c r="D4" t="n">
-        <v>12533</v>
+        <v>10933</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2360</v>
+        <v>693</v>
       </c>
       <c r="C5" t="n">
-        <v>5559</v>
+        <v>5942</v>
       </c>
       <c r="D5" t="n">
-        <v>6129</v>
+        <v>5584</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1205</v>
+        <v>265</v>
       </c>
       <c r="C6" t="n">
-        <v>4609</v>
+        <v>5066</v>
       </c>
       <c r="D6" t="n">
-        <v>1954</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>370</v>
+        <v>62</v>
       </c>
       <c r="C7" t="n">
-        <v>2815</v>
+        <v>2307</v>
       </c>
       <c r="D7" t="n">
-        <v>718</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1403</v>
+        <v>738</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>495</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>135</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>144</v>
+        <v>79</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>103</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3086</v>
+        <v>493</v>
       </c>
       <c r="C2" t="n">
-        <v>2353</v>
+        <v>6916</v>
       </c>
       <c r="D2" t="n">
-        <v>12835</v>
+        <v>6970</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3026</v>
+        <v>486</v>
       </c>
       <c r="C3" t="n">
-        <v>2330</v>
+        <v>2705</v>
       </c>
       <c r="D3" t="n">
-        <v>13905</v>
+        <v>10356</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3064</v>
+        <v>711</v>
       </c>
       <c r="C4" t="n">
-        <v>4130</v>
+        <v>4262</v>
       </c>
       <c r="D4" t="n">
-        <v>12522</v>
+        <v>10813</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2593</v>
+        <v>724</v>
       </c>
       <c r="C5" t="n">
-        <v>5397</v>
+        <v>5390</v>
       </c>
       <c r="D5" t="n">
-        <v>6859</v>
+        <v>6389</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1427</v>
+        <v>422</v>
       </c>
       <c r="C6" t="n">
-        <v>5119</v>
+        <v>5513</v>
       </c>
       <c r="D6" t="n">
-        <v>2369</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>372</v>
+        <v>134</v>
       </c>
       <c r="C7" t="n">
-        <v>3499</v>
+        <v>3685</v>
       </c>
       <c r="D7" t="n">
-        <v>831</v>
+        <v>838</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>1798</v>
+        <v>1498</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>625</v>
+        <v>487</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>197</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4324</v>
+        <v>479</v>
       </c>
       <c r="C2" t="n">
-        <v>5754</v>
+        <v>14412</v>
       </c>
       <c r="D2" t="n">
-        <v>15158</v>
+        <v>14815</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2560</v>
+        <v>405</v>
       </c>
       <c r="C3" t="n">
-        <v>2066</v>
+        <v>4182</v>
       </c>
       <c r="D3" t="n">
-        <v>12855</v>
+        <v>9155</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2676</v>
+        <v>531</v>
       </c>
       <c r="C4" t="n">
-        <v>3214</v>
+        <v>3366</v>
       </c>
       <c r="D4" t="n">
-        <v>12353</v>
+        <v>10301</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2521</v>
+        <v>648</v>
       </c>
       <c r="C5" t="n">
-        <v>4777</v>
+        <v>4663</v>
       </c>
       <c r="D5" t="n">
-        <v>7465</v>
+        <v>6959</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1724</v>
+        <v>514</v>
       </c>
       <c r="C6" t="n">
-        <v>5187</v>
+        <v>5394</v>
       </c>
       <c r="D6" t="n">
-        <v>2918</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>656</v>
+        <v>232</v>
       </c>
       <c r="C7" t="n">
-        <v>4148</v>
+        <v>4561</v>
       </c>
       <c r="D7" t="n">
-        <v>1033</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>143</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>2465</v>
+        <v>2504</v>
       </c>
       <c r="D8" t="n">
-        <v>485</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>1044</v>
+        <v>932</v>
       </c>
       <c r="D9" t="n">
-        <v>312</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>361</v>
+        <v>319</v>
       </c>
       <c r="D10" t="n">
-        <v>191</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>141</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>66</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5873</v>
+        <v>3158</v>
       </c>
       <c r="C2" t="n">
-        <v>3318</v>
+        <v>7668</v>
       </c>
       <c r="D2" t="n">
-        <v>7969</v>
+        <v>8161</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2993</v>
+        <v>1202</v>
       </c>
       <c r="C2" t="n">
-        <v>3131</v>
+        <v>12392</v>
       </c>
       <c r="D2" t="n">
-        <v>11035</v>
+        <v>12150</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3463</v>
+        <v>360</v>
       </c>
       <c r="C3" t="n">
-        <v>3178</v>
+        <v>7697</v>
       </c>
       <c r="D3" t="n">
-        <v>14143</v>
+        <v>9309</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3671</v>
+        <v>417</v>
       </c>
       <c r="C4" t="n">
-        <v>4693</v>
+        <v>3647</v>
       </c>
       <c r="D4" t="n">
-        <v>12867</v>
+        <v>9800</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1732</v>
+        <v>547</v>
       </c>
       <c r="C5" t="n">
-        <v>7170</v>
+        <v>3968</v>
       </c>
       <c r="D5" t="n">
-        <v>6847</v>
+        <v>7193</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>606</v>
+        <v>526</v>
       </c>
       <c r="C6" t="n">
-        <v>5234</v>
+        <v>5019</v>
       </c>
       <c r="D6" t="n">
-        <v>2329</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>132</v>
+        <v>315</v>
       </c>
       <c r="C7" t="n">
-        <v>2415</v>
+        <v>4873</v>
       </c>
       <c r="D7" t="n">
-        <v>617</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>1023</v>
+        <v>3369</v>
       </c>
       <c r="D8" t="n">
-        <v>305</v>
+        <v>519</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>353</v>
+        <v>1563</v>
       </c>
       <c r="D9" t="n">
-        <v>187</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>167</v>
+        <v>550</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>98</v>
+        <v>205</v>
       </c>
       <c r="D11" t="n">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6687</v>
+        <v>4116</v>
       </c>
       <c r="C2" t="n">
-        <v>3583</v>
+        <v>5574</v>
       </c>
       <c r="D2" t="n">
-        <v>18176</v>
+        <v>17981</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2495</v>
+        <v>1045</v>
       </c>
       <c r="C3" t="n">
-        <v>1698</v>
+        <v>3028</v>
       </c>
       <c r="D3" t="n">
-        <v>2041</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4995</v>
+        <v>2565</v>
       </c>
       <c r="C2" t="n">
-        <v>6370</v>
+        <v>3181</v>
       </c>
       <c r="D2" t="n">
-        <v>21401</v>
+        <v>24235</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3769</v>
+        <v>2187</v>
       </c>
       <c r="C3" t="n">
-        <v>2396</v>
+        <v>3915</v>
       </c>
       <c r="D3" t="n">
-        <v>4601</v>
+        <v>4463</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1117</v>
+        <v>510</v>
       </c>
       <c r="C4" t="n">
-        <v>1054</v>
+        <v>1937</v>
       </c>
       <c r="D4" t="n">
-        <v>1592</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5111</v>
+        <v>1562</v>
       </c>
       <c r="C2" t="n">
-        <v>4666</v>
+        <v>2952</v>
       </c>
       <c r="D2" t="n">
-        <v>23936</v>
+        <v>30160</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3595</v>
+        <v>1961</v>
       </c>
       <c r="C3" t="n">
-        <v>3949</v>
+        <v>2993</v>
       </c>
       <c r="D3" t="n">
-        <v>6957</v>
+        <v>7456</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2068</v>
+        <v>1181</v>
       </c>
       <c r="C4" t="n">
-        <v>1782</v>
+        <v>3093</v>
       </c>
       <c r="D4" t="n">
-        <v>2121</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>519</v>
+        <v>267</v>
       </c>
       <c r="C5" t="n">
-        <v>679</v>
+        <v>1215</v>
       </c>
       <c r="D5" t="n">
-        <v>1212</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5087</v>
+        <v>2620</v>
       </c>
       <c r="C2" t="n">
-        <v>5501</v>
+        <v>4580</v>
       </c>
       <c r="D2" t="n">
-        <v>31787</v>
+        <v>27104</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3545</v>
+        <v>1460</v>
       </c>
       <c r="C3" t="n">
-        <v>3757</v>
+        <v>2566</v>
       </c>
       <c r="D3" t="n">
-        <v>9048</v>
+        <v>10551</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2391</v>
+        <v>1358</v>
       </c>
       <c r="C4" t="n">
-        <v>2930</v>
+        <v>2971</v>
       </c>
       <c r="D4" t="n">
-        <v>2918</v>
+        <v>2973</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1079</v>
+        <v>613</v>
       </c>
       <c r="C5" t="n">
-        <v>1247</v>
+        <v>2235</v>
       </c>
       <c r="D5" t="n">
-        <v>1340</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>287</v>
+        <v>172</v>
       </c>
       <c r="C6" t="n">
-        <v>488</v>
+        <v>769</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>841</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5679</v>
+        <v>1729</v>
       </c>
       <c r="C2" t="n">
-        <v>4165</v>
+        <v>4672</v>
       </c>
       <c r="D2" t="n">
-        <v>33216</v>
+        <v>28035</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3140</v>
+        <v>1652</v>
       </c>
       <c r="C3" t="n">
-        <v>3819</v>
+        <v>3147</v>
       </c>
       <c r="D3" t="n">
-        <v>11164</v>
+        <v>12324</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1854</v>
+        <v>1221</v>
       </c>
       <c r="C4" t="n">
-        <v>2783</v>
+        <v>2659</v>
       </c>
       <c r="D4" t="n">
-        <v>3420</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>904</v>
+        <v>843</v>
       </c>
       <c r="C5" t="n">
-        <v>1555</v>
+        <v>2584</v>
       </c>
       <c r="D5" t="n">
-        <v>1286</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="C6" t="n">
-        <v>591</v>
+        <v>1520</v>
       </c>
       <c r="D6" t="n">
-        <v>765</v>
+        <v>889</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>269</v>
+        <v>535</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5828</v>
+        <v>3105</v>
       </c>
       <c r="C2" t="n">
-        <v>3395</v>
+        <v>12495</v>
       </c>
       <c r="D2" t="n">
-        <v>29903</v>
+        <v>35525</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3683</v>
+        <v>1396</v>
       </c>
       <c r="C3" t="n">
-        <v>3448</v>
+        <v>3415</v>
       </c>
       <c r="D3" t="n">
-        <v>14205</v>
+        <v>13962</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2202</v>
+        <v>1215</v>
       </c>
       <c r="C4" t="n">
-        <v>3371</v>
+        <v>2861</v>
       </c>
       <c r="D4" t="n">
-        <v>4951</v>
+        <v>5464</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1239</v>
+        <v>909</v>
       </c>
       <c r="C5" t="n">
-        <v>2265</v>
+        <v>2568</v>
       </c>
       <c r="D5" t="n">
-        <v>1664</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>570</v>
+        <v>515</v>
       </c>
       <c r="C6" t="n">
-        <v>1148</v>
+        <v>2024</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>970</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C7" t="n">
-        <v>455</v>
+        <v>1007</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>248</v>
+        <v>405</v>
       </c>
       <c r="D8" t="n">
-        <v>382</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5425</v>
+        <v>2686</v>
       </c>
       <c r="C2" t="n">
-        <v>3713</v>
+        <v>7496</v>
       </c>
       <c r="D2" t="n">
-        <v>22680</v>
+        <v>27701</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3900</v>
+        <v>2022</v>
       </c>
       <c r="C3" t="n">
-        <v>2980</v>
+        <v>6683</v>
       </c>
       <c r="D3" t="n">
-        <v>15933</v>
+        <v>15590</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2525</v>
+        <v>839</v>
       </c>
       <c r="C4" t="n">
-        <v>3312</v>
+        <v>4305</v>
       </c>
       <c r="D4" t="n">
-        <v>6529</v>
+        <v>5059</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1526</v>
+        <v>475</v>
       </c>
       <c r="C5" t="n">
-        <v>2844</v>
+        <v>1983</v>
       </c>
       <c r="D5" t="n">
-        <v>2244</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>822</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>1745</v>
+        <v>986</v>
       </c>
       <c r="D6" t="n">
-        <v>985</v>
+        <v>645</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>342</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>828</v>
+        <v>396</v>
       </c>
       <c r="D7" t="n">
-        <v>611</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>352</v>
+        <v>281</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
